--- a/🌓_3_In_The_Moment/📲_Press_Matters/🌊_Playing_Defence/🇮🇷_Data_Wars_IRGC_Edition/📊_iran_war_essential_infrastructure_cyber_timeline.xlsx
+++ b/🌓_3_In_The_Moment/📲_Press_Matters/🌊_Playing_Defence/🇮🇷_Data_Wars_IRGC_Edition/📊_iran_war_essential_infrastructure_cyber_timeline.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyber Timeline" sheetId="1" r:id="R7349bebe8c1f46ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cyber Timeline" sheetId="1" r:id="R9c20e7090f3849d0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CyberTimeline" displayName="CyberTimeline" ref="A1:AN75" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CyberTimeline" displayName="CyberTimeline" ref="A1:AN91" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="40">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Record Type"/>
@@ -495,21 +495,11 @@
       <x:c r="H2" t="str">
         <x:v>War baseline used by this pack: beginning of the US–Israeli military campaign against Iran; comparison point for subsequent cyber activity.</x:v>
       </x:c>
-      <x:c r="I2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="J2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="K2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="L2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="M2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="I2" t="str"/>
+      <x:c r="J2" t="str"/>
+      <x:c r="K2" t="str"/>
+      <x:c r="L2" t="str"/>
+      <x:c r="M2" t="str"/>
       <x:c r="N2" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -519,39 +509,21 @@
       <x:c r="P2" t="str">
         <x:v>None recorded.</x:v>
       </x:c>
-      <x:c r="Q2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="R2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="S2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="T2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="U2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="Q2" t="str"/>
+      <x:c r="R2" t="str"/>
+      <x:c r="S2" t="str"/>
+      <x:c r="T2" t="str"/>
+      <x:c r="U2" t="str"/>
       <x:c r="V2" t="str">
         <x:v>Direct baseline</x:v>
       </x:c>
-      <x:c r="W2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="X2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="Y2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="W2" t="str"/>
+      <x:c r="X2" t="str"/>
+      <x:c r="Y2" t="str"/>
       <x:c r="Z2" t="str">
         <x:v>Context only</x:v>
       </x:c>
-      <x:c r="AA2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="AA2" t="str"/>
       <x:c r="AB2" t="str"/>
       <x:c r="AC2" t="str">
         <x:v>Context row</x:v>
@@ -565,9 +537,7 @@
       <x:c r="AF2" t="str">
         <x:v>No material attribution change recorded.</x:v>
       </x:c>
-      <x:c r="AG2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="AG2" t="str"/>
       <x:c r="AH2" t="str">
         <x:v>Not reported / not applicable.</x:v>
       </x:c>
@@ -577,9 +547,7 @@
       <x:c r="AJ2" t="str">
         <x:v>⚪ Open / not established.</x:v>
       </x:c>
-      <x:c r="AK2" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="AK2" t="str"/>
       <x:c r="AL2" t="str">
         <x:v>No automatic IHL conclusion from wartime timing.</x:v>
       </x:c>
@@ -627,12 +595,8 @@
       <x:c r="L3" t="str">
         <x:v>Official assessment</x:v>
       </x:c>
-      <x:c r="M3" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="N3" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M3" t="str"/>
+      <x:c r="N3" t="str"/>
       <x:c r="O3" t="str">
         <x:v>Iran-linked hacktivist risk discussed; no incident attribution.</x:v>
       </x:c>
@@ -642,9 +606,7 @@
       <x:c r="Q3" t="str">
         <x:v>🟢 Established</x:v>
       </x:c>
-      <x:c r="R3" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="R3" t="str"/>
       <x:c r="S3" t="str">
         <x:v>⚪ Open</x:v>
       </x:c>
@@ -663,9 +625,7 @@
       <x:c r="X3" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="Y3" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="Y3" t="str"/>
       <x:c r="Z3" t="str">
         <x:v>Preparedness marker</x:v>
       </x:c>
@@ -1115,9 +1075,7 @@
       <x:c r="L7" t="str">
         <x:v>Officially reported incident</x:v>
       </x:c>
-      <x:c r="M7" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M7" t="str"/>
       <x:c r="N7" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -1237,9 +1195,7 @@
       <x:c r="L8" t="str">
         <x:v>Reported / alleged</x:v>
       </x:c>
-      <x:c r="M8" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M8" t="str"/>
       <x:c r="N8" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -1359,9 +1315,7 @@
       <x:c r="L9" t="str">
         <x:v>Officially reported incident</x:v>
       </x:c>
-      <x:c r="M9" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M9" t="str"/>
       <x:c r="N9" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -1481,9 +1435,7 @@
       <x:c r="L10" t="str">
         <x:v>Officially reported incident</x:v>
       </x:c>
-      <x:c r="M10" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M10" t="str"/>
       <x:c r="N10" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -1603,9 +1555,7 @@
       <x:c r="L11" t="str">
         <x:v>Researcher attribution</x:v>
       </x:c>
-      <x:c r="M11" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M11" t="str"/>
       <x:c r="N11" t="str">
         <x:v>Iran-backed / MOIS-linked actor per researchers</x:v>
       </x:c>
@@ -1725,9 +1675,7 @@
       <x:c r="L12" t="str">
         <x:v>Official aggregate assessment</x:v>
       </x:c>
-      <x:c r="M12" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M12" t="str"/>
       <x:c r="N12" t="str">
         <x:v>Multiple hostile-state actors</x:v>
       </x:c>
@@ -1740,15 +1688,11 @@
       <x:c r="Q12" t="str">
         <x:v>🟢 Established</x:v>
       </x:c>
-      <x:c r="R12" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="R12" t="str"/>
       <x:c r="S12" t="str">
         <x:v>🟢 Established for hostile-state aggregate; ⚪ Open for Iran share</x:v>
       </x:c>
-      <x:c r="T12" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="T12" t="str"/>
       <x:c r="U12" t="str">
         <x:v>🔴 Established hostile-state pressure</x:v>
       </x:c>
@@ -1785,9 +1729,7 @@
       <x:c r="AF12" t="str">
         <x:v>No material attribution change recorded.</x:v>
       </x:c>
-      <x:c r="AG12" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="AG12" t="str"/>
       <x:c r="AH12" t="str">
         <x:v>Not reported / not applicable.</x:v>
       </x:c>
@@ -1847,9 +1789,7 @@
       <x:c r="L13" t="str">
         <x:v>Official incident reporting / investigation</x:v>
       </x:c>
-      <x:c r="M13" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M13" t="str"/>
       <x:c r="N13" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -2091,9 +2031,7 @@
       <x:c r="L15" t="str">
         <x:v>Official/customer reporting</x:v>
       </x:c>
-      <x:c r="M15" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M15" t="str"/>
       <x:c r="N15" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -2329,15 +2267,11 @@
       <x:c r="J17" t="str">
         <x:v>No new operational effect; attribution assessment strengthened.</x:v>
       </x:c>
-      <x:c r="K17" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="K17" t="str"/>
       <x:c r="L17" t="str">
         <x:v>Reported investigative assessment</x:v>
       </x:c>
-      <x:c r="M17" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M17" t="str"/>
       <x:c r="N17" t="str">
         <x:v>Iranian / Iran-affiliated actor not publicly resolved to one operator</x:v>
       </x:c>
@@ -2350,9 +2284,7 @@
       <x:c r="Q17" t="str">
         <x:v>🟢 Established as attribution event</x:v>
       </x:c>
-      <x:c r="R17" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="R17" t="str"/>
       <x:c r="S17" t="str">
         <x:v>🟡 Probable</x:v>
       </x:c>
@@ -2457,9 +2389,7 @@
       <x:c r="L18" t="str">
         <x:v>Official warning / investigation</x:v>
       </x:c>
-      <x:c r="M18" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M18" t="str"/>
       <x:c r="N18" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -2573,15 +2503,11 @@
       <x:c r="J19" t="str">
         <x:v>No new operational effect; records a contested public attribution position.</x:v>
       </x:c>
-      <x:c r="K19" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="K19" t="str"/>
       <x:c r="L19" t="str">
         <x:v>Public political statement</x:v>
       </x:c>
-      <x:c r="M19" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M19" t="str"/>
       <x:c r="N19" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -2594,15 +2520,11 @@
       <x:c r="Q19" t="str">
         <x:v>🟢 Established as public-position event</x:v>
       </x:c>
-      <x:c r="R19" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="R19" t="str"/>
       <x:c r="S19" t="str">
         <x:v>⚪ Open</x:v>
       </x:c>
-      <x:c r="T19" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="T19" t="str"/>
       <x:c r="U19" t="str">
         <x:v>🔴 Pattern may exist independently of sponsor</x:v>
       </x:c>
@@ -2701,9 +2623,7 @@
       <x:c r="L20" t="str">
         <x:v>Official state reporting / FBI investigation</x:v>
       </x:c>
-      <x:c r="M20" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M20" t="str"/>
       <x:c r="N20" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -2817,15 +2737,11 @@
       <x:c r="J21" t="str">
         <x:v>No new operational effect in this row.</x:v>
       </x:c>
-      <x:c r="K21" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="K21" t="str"/>
       <x:c r="L21" t="str">
         <x:v>Reported intelligence assessment + contrary political statement</x:v>
       </x:c>
-      <x:c r="M21" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M21" t="str"/>
       <x:c r="N21" t="str">
         <x:v>Iranian actors assessed likely; exact operator unresolved publicly</x:v>
       </x:c>
@@ -2838,9 +2754,7 @@
       <x:c r="Q21" t="str">
         <x:v>🟢 Established as public-record conflict</x:v>
       </x:c>
-      <x:c r="R21" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="R21" t="str"/>
       <x:c r="S21" t="str">
         <x:v>🟡 Probable</x:v>
       </x:c>
@@ -2945,9 +2859,7 @@
       <x:c r="L22" t="str">
         <x:v>Campaign-level reporting</x:v>
       </x:c>
-      <x:c r="M22" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M22" t="str"/>
       <x:c r="N22" t="str">
         <x:v>Unknown / potentially multiple</x:v>
       </x:c>
@@ -3189,9 +3101,7 @@
       <x:c r="L24" t="str">
         <x:v>Officially reported incident; extortion demand reported</x:v>
       </x:c>
-      <x:c r="M24" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M24" t="str"/>
       <x:c r="N24" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -3311,9 +3221,7 @@
       <x:c r="L25" t="str">
         <x:v>Official compromise investigation + unverified Iranian-media technical claims</x:v>
       </x:c>
-      <x:c r="M25" t="str">
-        <x:v>None</x:v>
-      </x:c>
+      <x:c r="M25" t="str"/>
       <x:c r="N25" t="str">
         <x:v>Unknown foreign actor</x:v>
       </x:c>
@@ -3433,9 +3341,7 @@
       <x:c r="L26" t="str">
         <x:v>Affected-authority confirmation</x:v>
       </x:c>
-      <x:c r="M26" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M26" t="str"/>
       <x:c r="N26" t="str">
         <x:v>Unknown ransomware operator</x:v>
       </x:c>
@@ -3549,9 +3455,7 @@
       <x:c r="J27" t="str">
         <x:v>No new operational effect; material change in public attribution history.</x:v>
       </x:c>
-      <x:c r="K27" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="K27" t="str"/>
       <x:c r="L27" t="str">
         <x:v>📣 Actor-claimed</x:v>
       </x:c>
@@ -3570,9 +3474,7 @@
       <x:c r="Q27" t="str">
         <x:v>🟢 Established as claim event</x:v>
       </x:c>
-      <x:c r="R27" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="R27" t="str"/>
       <x:c r="S27" t="str">
         <x:v>🟡 Probable for Iran-linked Minnesota/core wave; formal attribution absent</x:v>
       </x:c>
@@ -3677,9 +3579,7 @@
       <x:c r="L28" t="str">
         <x:v>Officially reported incident</x:v>
       </x:c>
-      <x:c r="M28" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M28" t="str"/>
       <x:c r="N28" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -4043,12 +3943,8 @@
       <x:c r="L31" t="str">
         <x:v>Official preparedness disclosure reported</x:v>
       </x:c>
-      <x:c r="M31" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="N31" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M31" t="str"/>
+      <x:c r="N31" t="str"/>
       <x:c r="O31" t="str">
         <x:v>Not applicable to a new Connecticut incident.</x:v>
       </x:c>
@@ -4058,12 +3954,8 @@
       <x:c r="Q31" t="str">
         <x:v>N/A — no Connecticut incident reported</x:v>
       </x:c>
-      <x:c r="R31" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="S31" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="R31" t="str"/>
+      <x:c r="S31" t="str"/>
       <x:c r="T31" t="str">
         <x:v>🟢 Established response to wider water campaign</x:v>
       </x:c>
@@ -4079,9 +3971,7 @@
       <x:c r="X31" t="str">
         <x:v>Not applicable / context</x:v>
       </x:c>
-      <x:c r="Y31" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="Y31" t="str"/>
       <x:c r="Z31" t="str">
         <x:v>High governance significance because mitigation depends on component visibility.</x:v>
       </x:c>
@@ -4287,9 +4177,7 @@
       <x:c r="L33" t="str">
         <x:v>Official defensive advisory</x:v>
       </x:c>
-      <x:c r="M33" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M33" t="str"/>
       <x:c r="N33" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -4403,9 +4291,7 @@
       <x:c r="J34" t="str">
         <x:v>No new operational effect; prolonged public executive-level uncertainty.</x:v>
       </x:c>
-      <x:c r="K34" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="K34" t="str"/>
       <x:c r="L34" t="str">
         <x:v>Reported intelligence assessment + actor claim + divergent presidential position</x:v>
       </x:c>
@@ -4424,9 +4310,7 @@
       <x:c r="Q34" t="str">
         <x:v>🟢 Established as a governance event</x:v>
       </x:c>
-      <x:c r="R34" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="R34" t="str"/>
       <x:c r="S34" t="str">
         <x:v>🟡 Probable for Minnesota/core wave; formal attribution absent</x:v>
       </x:c>
@@ -4531,9 +4415,7 @@
       <x:c r="L35" t="str">
         <x:v>Officially confirmed federal investigation</x:v>
       </x:c>
-      <x:c r="M35" t="str">
-        <x:v>None</x:v>
-      </x:c>
+      <x:c r="M35" t="str"/>
       <x:c r="N35" t="str">
         <x:v>Unknown foreign actor(s)</x:v>
       </x:c>
@@ -4653,9 +4535,7 @@
       <x:c r="L36" t="str">
         <x:v>Government / media disclosure</x:v>
       </x:c>
-      <x:c r="M36" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M36" t="str"/>
       <x:c r="N36" t="str">
         <x:v>Suspected Iran-linked actor; specific group not publicly established</x:v>
       </x:c>
@@ -4775,9 +4655,7 @@
       <x:c r="L37" t="str">
         <x:v>Official campaign-scale disclosure</x:v>
       </x:c>
-      <x:c r="M37" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M37" t="str"/>
       <x:c r="N37" t="str">
         <x:v>Unknown / potentially multiple; Iranian responsibility reportedly favoured for much of core campaign</x:v>
       </x:c>
@@ -5263,9 +5141,7 @@
       <x:c r="L41" t="str">
         <x:v>Official operator disclosure</x:v>
       </x:c>
-      <x:c r="M41" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M41" t="str"/>
       <x:c r="N41" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -5507,9 +5383,7 @@
       <x:c r="L43" t="str">
         <x:v>Official state confirmation</x:v>
       </x:c>
-      <x:c r="M43" t="str">
-        <x:v>None</x:v>
-      </x:c>
+      <x:c r="M43" t="str"/>
       <x:c r="N43" t="str">
         <x:v>Unidentified foreign actor(s)</x:v>
       </x:c>
@@ -5751,9 +5625,7 @@
       <x:c r="L45" t="str">
         <x:v>Researcher / industry reporting</x:v>
       </x:c>
-      <x:c r="M45" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M45" t="str"/>
       <x:c r="N45" t="str">
         <x:v>Iranian-aligned actors</x:v>
       </x:c>
@@ -5873,9 +5745,7 @@
       <x:c r="L46" t="str">
         <x:v>Affected-operator disclosure</x:v>
       </x:c>
-      <x:c r="M46" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M46" t="str"/>
       <x:c r="N46" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -5995,9 +5865,7 @@
       <x:c r="L47" t="str">
         <x:v>Affected-authority assessment</x:v>
       </x:c>
-      <x:c r="M47" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M47" t="str"/>
       <x:c r="N47" t="str">
         <x:v>Unknown criminal / ransomware actor</x:v>
       </x:c>
@@ -6117,9 +5985,7 @@
       <x:c r="L48" t="str">
         <x:v>Campaign reporting</x:v>
       </x:c>
-      <x:c r="M48" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M48" t="str"/>
       <x:c r="N48" t="str">
         <x:v>Iranian government-linked hackers</x:v>
       </x:c>
@@ -6239,9 +6105,7 @@
       <x:c r="L49" t="str">
         <x:v>Official provider / court disclosure</x:v>
       </x:c>
-      <x:c r="M49" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M49" t="str"/>
       <x:c r="N49" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -6845,9 +6709,7 @@
       <x:c r="L54" t="str">
         <x:v>Technical research disclosure</x:v>
       </x:c>
-      <x:c r="M54" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M54" t="str"/>
       <x:c r="N54" t="str">
         <x:v>Likely Russian-speaking operator per GreyNoise</x:v>
       </x:c>
@@ -6967,9 +6829,7 @@
       <x:c r="L55" t="str">
         <x:v>Platform threat-intelligence assessment</x:v>
       </x:c>
-      <x:c r="M55" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="M55" t="str"/>
       <x:c r="N55" t="str">
         <x:v>Iran-nexus threat actor</x:v>
       </x:c>
@@ -7451,9 +7311,7 @@
       <x:c r="L59" t="str">
         <x:v>Government-official reporting / campaign watch</x:v>
       </x:c>
-      <x:c r="M59" t="str">
-        <x:v>None</x:v>
-      </x:c>
+      <x:c r="M59" t="str"/>
       <x:c r="N59" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -7573,9 +7431,7 @@
       <x:c r="L60" t="str">
         <x:v>Confirmed systems malfunction + crew-reported suspected cyberattack</x:v>
       </x:c>
-      <x:c r="M60" t="str">
-        <x:v>None</x:v>
-      </x:c>
+      <x:c r="M60" t="str"/>
       <x:c r="N60" t="str">
         <x:v>Unknown</x:v>
       </x:c>
@@ -7689,15 +7545,11 @@
       <x:c r="J61" t="str">
         <x:v>No new operational effect; records change in public acknowledgement and investigative posture.</x:v>
       </x:c>
-      <x:c r="K61" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="K61" t="str"/>
       <x:c r="L61" t="str">
         <x:v>Official acknowledgement + reported Iran investigation</x:v>
       </x:c>
-      <x:c r="M61" t="str">
-        <x:v>None</x:v>
-      </x:c>
+      <x:c r="M61" t="str"/>
       <x:c r="N61" t="str">
         <x:v>Unknown foreign actor(s)</x:v>
       </x:c>
@@ -7710,9 +7562,7 @@
       <x:c r="Q61" t="str">
         <x:v>🟢 Governance update established</x:v>
       </x:c>
-      <x:c r="R61" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="R61" t="str"/>
       <x:c r="S61" t="str">
         <x:v>🟠 Iran hypothesis under investigation; formal attribution absent</x:v>
       </x:c>
@@ -7846,9 +7696,7 @@
       <x:c r="W62" t="str">
         <x:v>No incident Iran attribution</x:v>
       </x:c>
-      <x:c r="X62" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="X62" t="str"/>
       <x:c r="Y62" t="str">
         <x:v>Preventive risk mitigation, not evidence of compromise.</x:v>
       </x:c>
@@ -7873,9 +7721,7 @@
       <x:c r="AF62" t="str">
         <x:v>25 September advisory → 28 September restoration</x:v>
       </x:c>
-      <x:c r="AG62" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
+      <x:c r="AG62" t="str"/>
       <x:c r="AH62" t="str">
         <x:v>Services temporarily shut as precaution</x:v>
       </x:c>
@@ -9434,10 +9280,1962 @@
         <x:v>Regulator aggregate; individual incident dates not public.</x:v>
       </x:c>
     </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str">
+        <x:v>2026-10-13</x:v>
+      </x:c>
+      <x:c r="B76" t="str">
+        <x:v>Cyber incident / supplier update</x:v>
+      </x:c>
+      <x:c r="C76" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D76" t="str">
+        <x:v>United Kingdom</x:v>
+      </x:c>
+      <x:c r="E76" t="str">
+        <x:v>Government complaints administration</x:v>
+      </x:c>
+      <x:c r="F76" t="str">
+        <x:v>Cyber incidents / cross-sector</x:v>
+      </x:c>
+      <x:c r="G76" t="str">
+        <x:v>Housing Ombudsman Service</x:v>
+      </x:c>
+      <x:c r="H76" t="str">
+        <x:v>External IT supplier incident disrupted case management, online complaint form, landlord portal and web chat; possible contact-data exposure under investigation.</x:v>
+      </x:c>
+      <x:c r="I76" t="str">
+        <x:v>Supplier-hosted case management</x:v>
+      </x:c>
+      <x:c r="J76" t="str">
+        <x:v>Digital complaints and case access disrupted.</x:v>
+      </x:c>
+      <x:c r="K76" t="str">
+        <x:v>Potential contact information exposure; scope open.</x:v>
+      </x:c>
+      <x:c r="L76" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M76" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N76" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O76" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P76" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q76" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R76" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S76" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T76" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U76" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V76" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W76" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X76" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y76" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z76" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA76" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB76" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC76" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD76" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE76" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF76" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG76" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH76" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI76" t="str">
+        <x:v>Malicious activity / shared access</x:v>
+      </x:c>
+      <x:c r="AJ76" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK76" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL76" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM76" t="str">
+        <x:v>Digital complaints and case access disrupted.</x:v>
+      </x:c>
+      <x:c r="AN76" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str">
+        <x:v>2026-10-15</x:v>
+      </x:c>
+      <x:c r="B77" t="str">
+        <x:v>Cyber incident / supplier disruption</x:v>
+      </x:c>
+      <x:c r="C77" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D77" t="str">
+        <x:v>United States</x:v>
+      </x:c>
+      <x:c r="E77" t="str">
+        <x:v>Federal justice administration</x:v>
+      </x:c>
+      <x:c r="F77" t="str">
+        <x:v>Cyber incidents / cross-sector</x:v>
+      </x:c>
+      <x:c r="G77" t="str">
+        <x:v>BAE Systems / US Bankruptcy Noticing Center</x:v>
+      </x:c>
+      <x:c r="H77" t="str">
+        <x:v>Cybersecurity incident at contractor reportedly disabled federal bankruptcy noticing websites and processes.</x:v>
+      </x:c>
+      <x:c r="I77" t="str">
+        <x:v>Outsourced federal court administrative IT</x:v>
+      </x:c>
+      <x:c r="J77" t="str">
+        <x:v>Official bankruptcy notice processes unavailable.</x:v>
+      </x:c>
+      <x:c r="K77" t="str">
+        <x:v>No established impact on defence programmes.</x:v>
+      </x:c>
+      <x:c r="L77" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M77" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N77" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O77" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P77" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q77" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R77" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S77" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T77" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U77" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V77" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W77" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X77" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y77" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z77" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA77" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB77" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC77" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD77" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE77" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF77" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG77" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH77" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI77" t="str">
+        <x:v>Malicious activity / shared access</x:v>
+      </x:c>
+      <x:c r="AJ77" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK77" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL77" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM77" t="str">
+        <x:v>Official bankruptcy notice processes unavailable.</x:v>
+      </x:c>
+      <x:c r="AN77" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="str">
+        <x:v>2026-10-15</x:v>
+      </x:c>
+      <x:c r="B78" t="str">
+        <x:v>Infrastructure availability incident</x:v>
+      </x:c>
+      <x:c r="C78" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D78" t="str">
+        <x:v>United Kingdom / United States</x:v>
+      </x:c>
+      <x:c r="E78" t="str">
+        <x:v>CDN / cloud</x:v>
+      </x:c>
+      <x:c r="F78" t="str">
+        <x:v>Shared infrastructure resilience</x:v>
+      </x:c>
+      <x:c r="G78" t="str">
+        <x:v>Cloudflare network services</x:v>
+      </x:c>
+      <x:c r="H78" t="str">
+        <x:v>London network-performance interruption and separately reported eastern-US issues; do not presume same cause.</x:v>
+      </x:c>
+      <x:c r="I78" t="str">
+        <x:v>CDN / distributed cloud</x:v>
+      </x:c>
+      <x:c r="J78" t="str">
+        <x:v>Short-lived service performance degradation reported.</x:v>
+      </x:c>
+      <x:c r="K78" t="str">
+        <x:v>No malicious cause established.</x:v>
+      </x:c>
+      <x:c r="L78" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M78" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N78" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O78" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P78" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q78" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R78" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S78" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T78" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U78" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V78" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W78" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X78" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y78" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z78" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA78" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB78" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC78" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD78" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE78" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF78" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG78" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH78" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI78" t="str">
+        <x:v>Non-malicious cascading dependency</x:v>
+      </x:c>
+      <x:c r="AJ78" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK78" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL78" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM78" t="str">
+        <x:v>Short-lived service performance degradation reported.</x:v>
+      </x:c>
+      <x:c r="AN78" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>Malicious activity / incident update</x:v>
+      </x:c>
+      <x:c r="C79" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D79" t="str">
+        <x:v>Netherlands / Belgium / United States</x:v>
+      </x:c>
+      <x:c r="E79" t="str">
+        <x:v>Food distribution / retail logistics</x:v>
+      </x:c>
+      <x:c r="F79" t="str">
+        <x:v>Cyber incidents / cross-sector</x:v>
+      </x:c>
+      <x:c r="G79" t="str">
+        <x:v>Ahold Delhaize / Albert Heijn / Delhaize / Stop &amp; Shop</x:v>
+      </x:c>
+      <x:c r="H79" t="str">
+        <x:v>Follow-up to 11 October incident: provider confirmed malicious IT activity; e-commerce and delivery disruption continued during phased restoration.</x:v>
+      </x:c>
+      <x:c r="I79" t="str">
+        <x:v>Retail IT / logistics / digital ordering</x:v>
+      </x:c>
+      <x:c r="J79" t="str">
+        <x:v>Online fulfilment and customer-facing services disrupted; physical shops generally remained open.</x:v>
+      </x:c>
+      <x:c r="K79" t="str">
+        <x:v>No confirmed data theft in supplied account.</x:v>
+      </x:c>
+      <x:c r="L79" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M79" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N79" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O79" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P79" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q79" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R79" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S79" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T79" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U79" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V79" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W79" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X79" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y79" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z79" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA79" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB79" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC79" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD79" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE79" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF79" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG79" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH79" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI79" t="str">
+        <x:v>Malicious activity / shared access</x:v>
+      </x:c>
+      <x:c r="AJ79" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK79" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL79" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM79" t="str">
+        <x:v>Online fulfilment and customer-facing services disrupted; physical shops generally remained open.</x:v>
+      </x:c>
+      <x:c r="AN79" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B80" t="str">
+        <x:v>Cyber incident / managed administration</x:v>
+      </x:c>
+      <x:c r="C80" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D80" t="str">
+        <x:v>Global / United Kingdom</x:v>
+      </x:c>
+      <x:c r="E80" t="str">
+        <x:v>Managed websites / backup</x:v>
+      </x:c>
+      <x:c r="F80" t="str">
+        <x:v>Cyber incidents / cross-sector</x:v>
+      </x:c>
+      <x:c r="G80" t="str">
+        <x:v>TeamUpdraft / UpdraftCentral</x:v>
+      </x:c>
+      <x:c r="H80" t="str">
+        <x:v>Reported compromise of trusted connection keys used to create accounts and install malicious plugins on connected websites; updated connections revoked.</x:v>
+      </x:c>
+      <x:c r="I80" t="str">
+        <x:v>Trusted remote site administration</x:v>
+      </x:c>
+      <x:c r="J80" t="str">
+        <x:v>Downstream website compromises reported; essential-service effects not established.</x:v>
+      </x:c>
+      <x:c r="K80" t="str">
+        <x:v>Extent of downstream compromise unresolved.</x:v>
+      </x:c>
+      <x:c r="L80" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M80" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N80" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O80" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P80" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q80" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R80" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S80" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T80" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U80" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V80" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W80" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X80" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y80" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z80" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA80" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB80" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC80" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD80" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE80" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF80" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG80" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH80" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI80" t="str">
+        <x:v>Malicious activity / shared access</x:v>
+      </x:c>
+      <x:c r="AJ80" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK80" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL80" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM80" t="str">
+        <x:v>Downstream website compromises reported; essential-service effects not established.</x:v>
+      </x:c>
+      <x:c r="AN80" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>Cloud identity intrusion / update</x:v>
+      </x:c>
+      <x:c r="C81" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D81" t="str">
+        <x:v>United States / international</x:v>
+      </x:c>
+      <x:c r="E81" t="str">
+        <x:v>Cloud backup / identity / strategic policy</x:v>
+      </x:c>
+      <x:c r="F81" t="str">
+        <x:v>Cyber incidents / cross-sector</x:v>
+      </x:c>
+      <x:c r="G81" t="str">
+        <x:v>ConnectWise Cloud Backup / Microsoft 365 customers</x:v>
+      </x:c>
+      <x:c r="H81" t="str">
+        <x:v>Application identity misuse and administrative persistence reported; strategic-sector targeting attempts described; distinguish attempts from successful access.</x:v>
+      </x:c>
+      <x:c r="I81" t="str">
+        <x:v>Cloud identity / application credentials / backup</x:v>
+      </x:c>
+      <x:c r="J81" t="str">
+        <x:v>Cloud backup, security monitoring and cloud-management functions suspended during remediation.</x:v>
+      </x:c>
+      <x:c r="K81" t="str">
+        <x:v>No confirmed compromise of specifically targeted national-security organisations.</x:v>
+      </x:c>
+      <x:c r="L81" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M81" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N81" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O81" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P81" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q81" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R81" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S81" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T81" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U81" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V81" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W81" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X81" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y81" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z81" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA81" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB81" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC81" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD81" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE81" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF81" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG81" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH81" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI81" t="str">
+        <x:v>Malicious activity / shared access</x:v>
+      </x:c>
+      <x:c r="AJ81" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK81" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL81" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM81" t="str">
+        <x:v>Cloud backup, security monitoring and cloud-management functions suspended during remediation.</x:v>
+      </x:c>
+      <x:c r="AN81" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="str">
+        <x:v>2026-10-19</x:v>
+      </x:c>
+      <x:c r="B82" t="str">
+        <x:v>Digital trust security advisory</x:v>
+      </x:c>
+      <x:c r="C82" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D82" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="E82" t="str">
+        <x:v>PKI / certificates / identity</x:v>
+      </x:c>
+      <x:c r="F82" t="str">
+        <x:v>Systemic vulnerability / defensive response</x:v>
+      </x:c>
+      <x:c r="G82" t="str">
+        <x:v>eMudhra intermediate certificate keys / Cloudflare advisory</x:v>
+      </x:c>
+      <x:c r="H82" t="str">
+        <x:v>Reported compromise of intermediate certificate private keys; exploitation and service consequences not established.</x:v>
+      </x:c>
+      <x:c r="I82" t="str">
+        <x:v>Certificate signing / PKI</x:v>
+      </x:c>
+      <x:c r="J82" t="str">
+        <x:v>No specific service outage established.</x:v>
+      </x:c>
+      <x:c r="K82" t="str">
+        <x:v>Potential trust and impersonation exposure; actual exploitation open.</x:v>
+      </x:c>
+      <x:c r="L82" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M82" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N82" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O82" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P82" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q82" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R82" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S82" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T82" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U82" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V82" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W82" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X82" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y82" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z82" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA82" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB82" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC82" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD82" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE82" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF82" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG82" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH82" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI82" t="str">
+        <x:v>Systemic exposure / emergency mitigation</x:v>
+      </x:c>
+      <x:c r="AJ82" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK82" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL82" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM82" t="str">
+        <x:v>No specific service outage established.</x:v>
+      </x:c>
+      <x:c r="AN82" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="B83" t="str">
+        <x:v>Non-malicious cloud outage</x:v>
+      </x:c>
+      <x:c r="C83" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D83" t="str">
+        <x:v>United Kingdom / Europe</x:v>
+      </x:c>
+      <x:c r="E83" t="str">
+        <x:v>Cloud / banking / payments / justice</x:v>
+      </x:c>
+      <x:c r="F83" t="str">
+        <x:v>Shared infrastructure resilience</x:v>
+      </x:c>
+      <x:c r="G83" t="str">
+        <x:v>Google Cloud London zone and downstream services</x:v>
+      </x:c>
+      <x:c r="H83" t="str">
+        <x:v>Reported London availability-zone power event disrupted cloud-hosted services; cross-sector effects require provider-by-provider causal verification.</x:v>
+      </x:c>
+      <x:c r="I83" t="str">
+        <x:v>Cloud availability zone / power dependency</x:v>
+      </x:c>
+      <x:c r="J83" t="str">
+        <x:v>Banking and payment access and remote court services disrupted; other downstream links not uniformly established.</x:v>
+      </x:c>
+      <x:c r="K83" t="str">
+        <x:v>No malicious intrusion established.</x:v>
+      </x:c>
+      <x:c r="L83" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M83" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N83" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O83" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P83" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q83" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R83" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S83" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T83" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U83" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V83" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W83" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X83" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y83" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z83" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA83" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB83" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC83" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD83" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE83" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF83" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG83" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH83" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI83" t="str">
+        <x:v>Non-malicious cascading dependency</x:v>
+      </x:c>
+      <x:c r="AJ83" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK83" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL83" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM83" t="str">
+        <x:v>Banking and payment access and remote court services disrupted; other downstream links not uniformly established.</x:v>
+      </x:c>
+      <x:c r="AN83" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="B84" t="str">
+        <x:v>Payment service incident / status notices</x:v>
+      </x:c>
+      <x:c r="C84" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D84" t="str">
+        <x:v>United Kingdom / Europe / Brazil</x:v>
+      </x:c>
+      <x:c r="E84" t="str">
+        <x:v>Payments / banking</x:v>
+      </x:c>
+      <x:c r="F84" t="str">
+        <x:v>Shared infrastructure resilience</x:v>
+      </x:c>
+      <x:c r="G84" t="str">
+        <x:v>Stripe / Revolut Pay / PayByBank / Adyen</x:v>
+      </x:c>
+      <x:c r="H84" t="str">
+        <x:v>Reported payment-method authorisation, 3DS and PayByBank issues around 20 October; separate Adyen maintenance and Brazil Pix refund delays 21 October.</x:v>
+      </x:c>
+      <x:c r="I84" t="str">
+        <x:v>Payment processing / upstream partner dependencies</x:v>
+      </x:c>
+      <x:c r="J84" t="str">
+        <x:v>Some payment authorisations, settlement or refunds degraded; not a general payment-system failure.</x:v>
+      </x:c>
+      <x:c r="K84" t="str">
+        <x:v>Common cause across notices not established.</x:v>
+      </x:c>
+      <x:c r="L84" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M84" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N84" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O84" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P84" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q84" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R84" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S84" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T84" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U84" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V84" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W84" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X84" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y84" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z84" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA84" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB84" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC84" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD84" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE84" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF84" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG84" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH84" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI84" t="str">
+        <x:v>Non-malicious cascading dependency</x:v>
+      </x:c>
+      <x:c r="AJ84" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK84" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL84" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM84" t="str">
+        <x:v>Some payment authorisations, settlement or refunds degraded; not a general payment-system failure.</x:v>
+      </x:c>
+      <x:c r="AN84" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="str">
+        <x:v>2026-10-20</x:v>
+      </x:c>
+      <x:c r="B85" t="str">
+        <x:v>Retrospective ransomware advisory</x:v>
+      </x:c>
+      <x:c r="C85" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D85" t="str">
+        <x:v>Multinational</x:v>
+      </x:c>
+      <x:c r="E85" t="str">
+        <x:v>Critical infrastructure / enterprise IT / backup</x:v>
+      </x:c>
+      <x:c r="F85" t="str">
+        <x:v>Cyber incidents / cross-sector</x:v>
+      </x:c>
+      <x:c r="G85" t="str">
+        <x:v>SafePay ransomware campaign</x:v>
+      </x:c>
+      <x:c r="H85" t="str">
+        <x:v>Reported joint advisory assessed at least 600 victims since 2024; credential/VPN entry and interference with recovery systems. Historical victim count not new October attacks.</x:v>
+      </x:c>
+      <x:c r="I85" t="str">
+        <x:v>VPN / ransomware / backup</x:v>
+      </x:c>
+      <x:c r="J85" t="str">
+        <x:v>Encryption, extortion and recovery disruption across reported historical victims; per-sector service impact varies.</x:v>
+      </x:c>
+      <x:c r="K85" t="str">
+        <x:v>State sponsorship not established.</x:v>
+      </x:c>
+      <x:c r="L85" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M85" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O85" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P85" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q85" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R85" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S85" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T85" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U85" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V85" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W85" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X85" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y85" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z85" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA85" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB85" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC85" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD85" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE85" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF85" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG85" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH85" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI85" t="str">
+        <x:v>Malicious activity / shared access</x:v>
+      </x:c>
+      <x:c r="AJ85" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK85" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL85" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM85" t="str">
+        <x:v>Encryption, extortion and recovery disruption across reported historical victims; per-sector service impact varies.</x:v>
+      </x:c>
+      <x:c r="AN85" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="str">
+        <x:v>2026-10-21</x:v>
+      </x:c>
+      <x:c r="B86" t="str">
+        <x:v>Systemic vulnerability / defensive shutdown</x:v>
+      </x:c>
+      <x:c r="C86" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D86" t="str">
+        <x:v>Global / United Kingdom / Japan</x:v>
+      </x:c>
+      <x:c r="E86" t="str">
+        <x:v>PHP / government / healthcare / finance / transport / public warning</x:v>
+      </x:c>
+      <x:c r="F86" t="str">
+        <x:v>Systemic vulnerability / defensive response</x:v>
+      </x:c>
+      <x:c r="G86" t="str">
+        <x:v>PHP2Shell / PHP server deployments</x:v>
+      </x:c>
+      <x:c r="H86" t="str">
+        <x:v>Prior watch reports CVE-2026-109618 and CVE-2026-109619, emergency fixes, pre-disclosure honeypot exploit attempts and precautionary Japanese service suspensions including mobile emergency alerts; identifiers and effects require primary-source verification.</x:v>
+      </x:c>
+      <x:c r="I86" t="str">
+        <x:v>PHP web runtime / application servers</x:v>
+      </x:c>
+      <x:c r="J86" t="str">
+        <x:v>Reported defensive website, online banking, transport and public-warning service shutdowns; not evidence of compromise.</x:v>
+      </x:c>
+      <x:c r="K86" t="str">
+        <x:v>Successful exploitation of production essential services unestablished.</x:v>
+      </x:c>
+      <x:c r="L86" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M86" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N86" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O86" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P86" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q86" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R86" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S86" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T86" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U86" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V86" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W86" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X86" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y86" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z86" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA86" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB86" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC86" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD86" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE86" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF86" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG86" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH86" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI86" t="str">
+        <x:v>Systemic exposure / emergency mitigation</x:v>
+      </x:c>
+      <x:c r="AJ86" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK86" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL86" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM86" t="str">
+        <x:v>Reported defensive website, online banking, transport and public-warning service shutdowns; not evidence of compromise.</x:v>
+      </x:c>
+      <x:c r="AN86" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str">
+        <x:v>2026-10-21</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>Systemic vulnerability / vendor advisory</x:v>
+      </x:c>
+      <x:c r="C87" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D87" t="str">
+        <x:v>Global / European Union</x:v>
+      </x:c>
+      <x:c r="E87" t="str">
+        <x:v>Software development / CI-CD</x:v>
+      </x:c>
+      <x:c r="F87" t="str">
+        <x:v>Systemic vulnerability / defensive response</x:v>
+      </x:c>
+      <x:c r="G87" t="str">
+        <x:v>GitLab self-managed</x:v>
+      </x:c>
+      <x:c r="H87" t="str">
+        <x:v>Reported critical GitLab RCE advisory CVE-2026-110264 and vendor fixes; identifier, affected versions and CERT-EU notice require primary-source recheck.</x:v>
+      </x:c>
+      <x:c r="I87" t="str">
+        <x:v>Source control / CI-CD</x:v>
+      </x:c>
+      <x:c r="J87" t="str">
+        <x:v>No confirmed service outage or successful exploitation in supplied account.</x:v>
+      </x:c>
+      <x:c r="K87" t="str">
+        <x:v>Exposure potential, not established intrusion.</x:v>
+      </x:c>
+      <x:c r="L87" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M87" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N87" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O87" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P87" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q87" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R87" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S87" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T87" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U87" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V87" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W87" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X87" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y87" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z87" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA87" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB87" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC87" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD87" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE87" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF87" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG87" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH87" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI87" t="str">
+        <x:v>Systemic exposure / emergency mitigation</x:v>
+      </x:c>
+      <x:c r="AJ87" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK87" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL87" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM87" t="str">
+        <x:v>No confirmed service outage or successful exploitation in supplied account.</x:v>
+      </x:c>
+      <x:c r="AN87" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str">
+        <x:v>2026-10-21</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>Software supply chain compromise</x:v>
+      </x:c>
+      <x:c r="C88" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D88" t="str">
+        <x:v>Global</x:v>
+      </x:c>
+      <x:c r="E88" t="str">
+        <x:v>AI gateway / cloud secrets / software supply</x:v>
+      </x:c>
+      <x:c r="F88" t="str">
+        <x:v>Cyber incidents / cross-sector</x:v>
+      </x:c>
+      <x:c r="G88" t="str">
+        <x:v>LiteLLM PyPI and Docker distribution</x:v>
+      </x:c>
+      <x:c r="H88" t="str">
+        <x:v>Reported malicious LiteLLM 1.107.0 release distributed through compromised pipeline; downstream essential-service victims unknown.</x:v>
+      </x:c>
+      <x:c r="I88" t="str">
+        <x:v>Package distribution / release credentials</x:v>
+      </x:c>
+      <x:c r="J88" t="str">
+        <x:v>Potential credential theft and downstream code execution; no confirmed essential-service outage.</x:v>
+      </x:c>
+      <x:c r="K88" t="str">
+        <x:v>Package distribution not equivalent to downstream compromise.</x:v>
+      </x:c>
+      <x:c r="L88" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M88" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N88" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O88" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P88" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q88" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R88" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S88" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T88" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U88" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V88" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W88" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X88" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y88" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z88" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA88" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB88" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC88" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD88" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE88" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF88" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG88" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH88" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI88" t="str">
+        <x:v>Malicious activity / shared access</x:v>
+      </x:c>
+      <x:c r="AJ88" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK88" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL88" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM88" t="str">
+        <x:v>Potential credential theft and downstream code execution; no confirmed essential-service outage.</x:v>
+      </x:c>
+      <x:c r="AN88" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str">
+        <x:v>2026-10-22</x:v>
+      </x:c>
+      <x:c r="B89" t="str">
+        <x:v>Cyber incident / impact update</x:v>
+      </x:c>
+      <x:c r="C89" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D89" t="str">
+        <x:v>Japan</x:v>
+      </x:c>
+      <x:c r="E89" t="str">
+        <x:v>Cloud hosting / financial trading</x:v>
+      </x:c>
+      <x:c r="F89" t="str">
+        <x:v>Cyber incidents / cross-sector</x:v>
+      </x:c>
+      <x:c r="G89" t="str">
+        <x:v>GMO Onamae.com Desktop Cloud</x:v>
+      </x:c>
+      <x:c r="H89" t="str">
+        <x:v>Malware found on some hosted customer servers; provider suspended plans reportedly encompassing up to 26,739 servers; customer reports of unauthorised trading.</x:v>
+      </x:c>
+      <x:c r="I89" t="str">
+        <x:v>Hosted desktops / customer trading credentials</x:v>
+      </x:c>
+      <x:c r="J89" t="str">
+        <x:v>Cloud-hosting plans suspended; reported trading-account consequences.</x:v>
+      </x:c>
+      <x:c r="K89" t="str">
+        <x:v>26,739 potentially affected servers not verified compromised; losses unknown.</x:v>
+      </x:c>
+      <x:c r="L89" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M89" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N89" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O89" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P89" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q89" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R89" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S89" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T89" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U89" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V89" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W89" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X89" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y89" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z89" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA89" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB89" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC89" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD89" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE89" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF89" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG89" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH89" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI89" t="str">
+        <x:v>Malicious activity / shared access</x:v>
+      </x:c>
+      <x:c r="AJ89" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK89" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL89" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM89" t="str">
+        <x:v>Cloud-hosting plans suspended; reported trading-account consequences.</x:v>
+      </x:c>
+      <x:c r="AN89" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str">
+        <x:v>2026-10-14</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>Incident scope update</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D90" t="str">
+        <x:v>France</x:v>
+      </x:c>
+      <x:c r="E90" t="str">
+        <x:v>Food cold chain / refrigeration OT</x:v>
+      </x:c>
+      <x:c r="F90" t="str">
+        <x:v>Cyber incidents / cross-sector</x:v>
+      </x:c>
+      <x:c r="G90" t="str">
+        <x:v>Internet-connected supermarket refrigeration controllers</x:v>
+      </x:c>
+      <x:c r="H90" t="str">
+        <x:v>Follow-up to 11 October event: reports of around 700 supermarkets affected by controller compromise and defrost/temperature manipulation; verify site-specific physical impacts.</x:v>
+      </x:c>
+      <x:c r="I90" t="str">
+        <x:v>Refrigeration OT / remote controllers</x:v>
+      </x:c>
+      <x:c r="J90" t="str">
+        <x:v>Reported widespread cold-chain disruption and spoilage.</x:v>
+      </x:c>
+      <x:c r="K90" t="str">
+        <x:v>Some reported fires and temperature extremes require site-level corroboration.</x:v>
+      </x:c>
+      <x:c r="L90" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M90" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N90" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O90" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P90" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q90" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R90" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S90" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T90" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U90" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V90" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W90" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X90" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y90" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z90" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA90" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB90" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC90" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD90" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE90" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF90" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG90" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH90" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI90" t="str">
+        <x:v>Malicious activity / shared access</x:v>
+      </x:c>
+      <x:c r="AJ90" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK90" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL90" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM90" t="str">
+        <x:v>Reported widespread cold-chain disruption and spoilage.</x:v>
+      </x:c>
+      <x:c r="AN90" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str">
+        <x:v>2026-10-15</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>Retrospective breach scope update</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>Provisional / source recheck</x:v>
+      </x:c>
+      <x:c r="D91" t="str">
+        <x:v>United States — Texas</x:v>
+      </x:c>
+      <x:c r="E91" t="str">
+        <x:v>Energy utility / customer data</x:v>
+      </x:c>
+      <x:c r="F91" t="str">
+        <x:v>Cyber incidents / cross-sector</x:v>
+      </x:c>
+      <x:c r="G91" t="str">
+        <x:v>CenterPoint Energy</x:v>
+      </x:c>
+      <x:c r="H91" t="str">
+        <x:v>October regulatory update reportedly quantified 1,062,060 residents affected by earlier September customer-data breach; no new October attack.</x:v>
+      </x:c>
+      <x:c r="I91" t="str">
+        <x:v>Customer-facing utility data systems</x:v>
+      </x:c>
+      <x:c r="J91" t="str">
+        <x:v>No electricity or gas delivery disruption reported.</x:v>
+      </x:c>
+      <x:c r="K91" t="str">
+        <x:v>Customer PII exposure; not grid compromise.</x:v>
+      </x:c>
+      <x:c r="L91" t="str">
+        <x:v>Reported in supplied watch notes; independent verification pending</x:v>
+      </x:c>
+      <x:c r="M91" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="N91" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O91" t="str">
+        <x:v>Not established</x:v>
+      </x:c>
+      <x:c r="P91" t="str">
+        <x:v>None established</x:v>
+      </x:c>
+      <x:c r="Q91" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="R91" t="str">
+        <x:v>🟠 Developing — source recheck</x:v>
+      </x:c>
+      <x:c r="S91" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="T91" t="str">
+        <x:v>⚪ Open</x:v>
+      </x:c>
+      <x:c r="U91" t="str">
+        <x:v>🟡 Possible recurrence / shared dependency (not coordinated campaign)</x:v>
+      </x:c>
+      <x:c r="V91" t="str">
+        <x:v>Contextual / systemic relevance; not evidence of Iranian operation</x:v>
+      </x:c>
+      <x:c r="W91" t="str">
+        <x:v>No established Iranian connection</x:v>
+      </x:c>
+      <x:c r="X91" t="str">
+        <x:v>Open / no public Iran evidence</x:v>
+      </x:c>
+      <x:c r="Y91" t="str">
+        <x:v>Criminal or opportunistic activity; unrelated provider failure; defensive isolation; independent actors. Assess per event.</x:v>
+      </x:c>
+      <x:c r="Z91" t="str">
+        <x:v>Provisional: see incident-specific operational effect</x:v>
+      </x:c>
+      <x:c r="AA91" t="str">
+        <x:v>No established Iranian sponsorship or common operator; reported figures and technical identifiers pending primary-source review.</x:v>
+      </x:c>
+      <x:c r="AB91" t="str">
+        <x:v>Supplied 16–23 October watch notes and updated Markdown chronology; primary-source links to reconcile</x:v>
+      </x:c>
+      <x:c r="AC91" t="str">
+        <x:v>Provisional — secondary synthesis of prior watch; verify primary sources</x:v>
+      </x:c>
+      <x:c r="AD91" t="str">
+        <x:v>2026-10-23</x:v>
+      </x:c>
+      <x:c r="AE91" t="str">
+        <x:v>New provisional row / verification required</x:v>
+      </x:c>
+      <x:c r="AF91" t="str">
+        <x:v>No new Iranian attribution established</x:v>
+      </x:c>
+      <x:c r="AG91" t="str">
+        <x:v>Open / no evidence</x:v>
+      </x:c>
+      <x:c r="AH91" t="str">
+        <x:v>Not established / not applicable</x:v>
+      </x:c>
+      <x:c r="AI91" t="str">
+        <x:v>Malicious activity / shared access</x:v>
+      </x:c>
+      <x:c r="AJ91" t="str">
+        <x:v>⚪ Open / not established</x:v>
+      </x:c>
+      <x:c r="AK91" t="str">
+        <x:v>⚪ Open / no common campaign established</x:v>
+      </x:c>
+      <x:c r="AL91" t="str">
+        <x:v>Sector-specific review; no automatic legal conclusion</x:v>
+      </x:c>
+      <x:c r="AM91" t="str">
+        <x:v>No electricity or gas delivery disruption reported.</x:v>
+      </x:c>
+      <x:c r="AN91" t="str">
+        <x:v>Prior watch summary, not independently corroborated for this update; do not treat repeated summaries as independent sources.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd90ce9a44ecc4d49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R430d5af6087e4426"/>
   </x:tableParts>
 </x:worksheet>
 </file>